--- a/Referencing.xlsx
+++ b/Referencing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4EDB9C-359B-4970-ACF9-FE089DF16BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50979BF9-16E7-4915-A609-9A85DC17857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{8C8BEDCA-722A-43A6-AE3E-00839DBDC5D2}"/>
   </bookViews>
